--- a/RaidenDemo/文档/配置表/StageWaveResource.xlsx
+++ b/RaidenDemo/文档/配置表/StageWaveResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R39abb5414f1c40ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8abb3616589244f9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2697,6 +2697,33 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="7"/>
+      <x:c r="B56" s="7" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C56" s="7" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D56" s="7" t="str">
+        <x:v>直线</x:v>
+      </x:c>
+      <x:c r="E56" s="7" t="str">
+        <x:v>横向编队</x:v>
+      </x:c>
+      <x:c r="F56" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G56" s="8" t="str">
+        <x:v>360,80</x:v>
+      </x:c>
+      <x:c r="H56" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I56" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="D4:D1048576">
@@ -2713,6 +2740,6 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1ad6a4293af434b"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dba9878c1714d6d"/>
 </x:worksheet>
 </file>
--- a/RaidenDemo/文档/配置表/StageWaveResource.xlsx
+++ b/RaidenDemo/文档/配置表/StageWaveResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8abb3616589244f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R118412900882490d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2699,30 +2699,14 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="7"/>
-      <x:c r="B56" s="7" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C56" s="7" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D56" s="7" t="str">
-        <x:v>直线</x:v>
-      </x:c>
-      <x:c r="E56" s="7" t="str">
-        <x:v>横向编队</x:v>
-      </x:c>
-      <x:c r="F56" s="7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G56" s="8" t="str">
-        <x:v>360,80</x:v>
-      </x:c>
-      <x:c r="H56" s="7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I56" s="7" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B56" s="7"/>
+      <x:c r="C56" s="7"/>
+      <x:c r="D56" s="7"/>
+      <x:c r="E56" s="7"/>
+      <x:c r="F56" s="7"/>
+      <x:c r="G56" s="8"/>
+      <x:c r="H56" s="7"/>
+      <x:c r="I56" s="7"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="4">
@@ -2740,6 +2724,6 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dba9878c1714d6d"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c7df9f63c5c4862"/>
 </x:worksheet>
 </file>
--- a/RaidenDemo/文档/配置表/StageWaveResource.xlsx
+++ b/RaidenDemo/文档/配置表/StageWaveResource.xlsx
@@ -729,7 +729,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -758,6 +758,12 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="27" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="27" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="24" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1204,6 +1210,13 @@
     <x:col min="9" max="9" width="17.625" customWidth="1"/>
     <x:col min="10" max="11" width="15" customWidth="1"/>
     <x:col min="12" max="13" width="13" customWidth="1"/>
+    <x:col min="10" max="10" width="22" customWidth="1"/>
+    <x:col min="11" max="11" width="19" customWidth="1"/>
+    <x:col min="12" max="12" width="18" customWidth="1"/>
+    <x:col min="13" max="13" width="18" customWidth="1"/>
+    <x:col min="14" max="14" width="20" customWidth="1"/>
+    <x:col min="15" max="15" width="18" customWidth="1"/>
+    <x:col min="16" max="16" width="18" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="20" customHeight="1">
@@ -1234,6 +1247,41 @@
       <x:c r="I1" s="9" t="s">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>entrySpeedMultiplier</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>prepareDurationMs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>attackDurationMs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>patrolAmplitude</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>stationHeightRatio</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>exitDirection</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>rewardItemId</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="2" ht="20" customHeight="1">
       <x:c r="A2" s="10" t="s">
@@ -1263,6 +1311,41 @@
       <x:c r="I2" s="10" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="J2" s="10" t="inlineStr">
+        <x:is>
+          <x:t>入场速度倍率</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K2" s="10" t="inlineStr">
+        <x:is>
+          <x:t>开火准备毫秒</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L2" s="10" t="inlineStr">
+        <x:is>
+          <x:t>攻击阶段毫秒</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M2" s="10" t="inlineStr">
+        <x:is>
+          <x:t>巡航幅度</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N2" s="10" t="inlineStr">
+        <x:is>
+          <x:t>停留高度比例</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O2" s="10" t="inlineStr">
+        <x:is>
+          <x:t>撤离方向</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P2" s="10" t="inlineStr">
+        <x:is>
+          <x:t>全灭奖励道具ID（0为无）</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="3" ht="20" customHeight="1">
       <x:c r="A3" s="10" t="s">
@@ -1291,6 +1374,41 @@
       </x:c>
       <x:c r="I3" s="10" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="inlineStr">
+        <x:is>
+          <x:t>float</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K3" s="10" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L3" s="10" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M3" s="10" t="inlineStr">
+        <x:is>
+          <x:t>float</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N3" s="10" t="inlineStr">
+        <x:is>
+          <x:t>float</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O3" s="10" t="inlineStr">
+        <x:is>
+          <x:t>vector2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P3" s="10" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4" ht="20" customHeight="1">
@@ -1301,14 +1419,16 @@
       <x:c r="C4" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D4" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E4" s="11" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F4" s="11">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G4" s="11" t="s">
         <x:v>26</x:v>
@@ -1317,6 +1437,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I4" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J4" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K4" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L4" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M4" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N4" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O4" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P4" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1328,14 +1471,16 @@
       <x:c r="C5" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D5" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E5" s="11" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="11">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G5" s="11" t="s">
         <x:v>29</x:v>
@@ -1345,6 +1490,29 @@
       </x:c>
       <x:c r="I5" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J5" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K5" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L5" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M5" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N5" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O5" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P5" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20" customHeight="1">
@@ -1355,14 +1523,16 @@
       <x:c r="C6" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D6" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E6" s="11" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="11">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
         <x:v>31</x:v>
@@ -1372,6 +1542,29 @@
       </x:c>
       <x:c r="I6" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J6" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K6" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L6" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M6" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N6" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O6" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P6" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
@@ -1382,14 +1575,16 @@
       <x:c r="C7" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>32</x:v>
+      <x:c r="D7" s="11" t="inlineStr">
+        <x:is>
+          <x:t>巡航攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E7" s="11" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F7" s="11">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G7" s="11" t="s">
         <x:v>33</x:v>
@@ -1399,6 +1594,29 @@
       </x:c>
       <x:c r="I7" s="11">
         <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J7" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K7" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L7" s="11">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="M7" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N7" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O7" s="12" t="inlineStr">
+        <x:is>
+          <x:t>-0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P7" s="11">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="20" customHeight="1">
@@ -1409,8 +1627,10 @@
       <x:c r="C8" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D8" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E8" s="11" t="s">
         <x:v>25</x:v>
@@ -1425,6 +1645,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I8" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K8" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L8" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M8" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N8" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O8" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P8" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1436,8 +1679,10 @@
       <x:c r="C9" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D9" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E9" s="11" t="s">
         <x:v>28</x:v>
@@ -1453,6 +1698,29 @@
       </x:c>
       <x:c r="I9" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K9" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L9" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M9" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N9" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O9" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P9" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="20" customHeight="1">
@@ -1463,8 +1731,10 @@
       <x:c r="C10" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D10" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D10" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E10" s="11" t="s">
         <x:v>25</x:v>
@@ -1480,6 +1750,29 @@
       </x:c>
       <x:c r="I10" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J10" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K10" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L10" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M10" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N10" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O10" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P10" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="20" customHeight="1">
@@ -1490,8 +1783,10 @@
       <x:c r="C11" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D11" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E11" s="11" t="s">
         <x:v>25</x:v>
@@ -1506,6 +1801,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I11" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K11" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L11" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M11" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N11" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O11" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P11" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1517,8 +1835,10 @@
       <x:c r="C12" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D12" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D12" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E12" s="11" t="s">
         <x:v>28</x:v>
@@ -1534,6 +1854,29 @@
       </x:c>
       <x:c r="I12" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K12" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L12" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M12" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N12" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O12" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P12" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20" customHeight="1">
@@ -1544,8 +1887,10 @@
       <x:c r="C13" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D13" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D13" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E13" s="11" t="s">
         <x:v>25</x:v>
@@ -1561,6 +1906,29 @@
       </x:c>
       <x:c r="I13" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K13" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L13" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M13" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N13" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O13" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P13" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="20" customHeight="1">
@@ -1571,8 +1939,10 @@
       <x:c r="C14" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="s">
-        <x:v>32</x:v>
+      <x:c r="D14" s="11" t="inlineStr">
+        <x:is>
+          <x:t>巡航攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E14" s="11" t="s">
         <x:v>25</x:v>
@@ -1588,6 +1958,29 @@
       </x:c>
       <x:c r="I14" s="11">
         <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J14" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K14" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L14" s="11">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="M14" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N14" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O14" s="12" t="inlineStr">
+        <x:is>
+          <x:t>-0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P14" s="11">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="20" customHeight="1">
@@ -1598,8 +1991,10 @@
       <x:c r="C15" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D15" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E15" s="11" t="s">
         <x:v>25</x:v>
@@ -1614,6 +2009,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I15" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K15" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L15" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M15" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N15" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O15" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P15" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1625,8 +2043,10 @@
       <x:c r="C16" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D16" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E16" s="11" t="s">
         <x:v>28</x:v>
@@ -1642,6 +2062,29 @@
       </x:c>
       <x:c r="I16" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K16" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L16" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M16" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N16" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O16" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P16" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="20" customHeight="1">
@@ -1652,8 +2095,10 @@
       <x:c r="C17" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D17" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D17" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E17" s="11" t="s">
         <x:v>25</x:v>
@@ -1669,6 +2114,29 @@
       </x:c>
       <x:c r="I17" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K17" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L17" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M17" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N17" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O17" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P17" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="20" customHeight="1">
@@ -1679,8 +2147,10 @@
       <x:c r="C18" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D18" s="11" t="s">
-        <x:v>32</x:v>
+      <x:c r="D18" s="11" t="inlineStr">
+        <x:is>
+          <x:t>巡航攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E18" s="11" t="s">
         <x:v>25</x:v>
@@ -1696,6 +2166,29 @@
       </x:c>
       <x:c r="I18" s="11">
         <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J18" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K18" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L18" s="11">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="M18" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N18" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O18" s="12" t="inlineStr">
+        <x:is>
+          <x:t>-0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P18" s="11">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="20" customHeight="1">
@@ -1706,8 +2199,10 @@
       <x:c r="C19" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D19" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D19" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E19" s="11" t="s">
         <x:v>25</x:v>
@@ -1722,6 +2217,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I19" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K19" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L19" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M19" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N19" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O19" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P19" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1733,8 +2251,10 @@
       <x:c r="C20" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D20" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E20" s="11" t="s">
         <x:v>28</x:v>
@@ -1750,6 +2270,29 @@
       </x:c>
       <x:c r="I20" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J20" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K20" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L20" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M20" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N20" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O20" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P20" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="20" customHeight="1">
@@ -1760,8 +2303,10 @@
       <x:c r="C21" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D21" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E21" s="11" t="s">
         <x:v>25</x:v>
@@ -1777,6 +2322,29 @@
       </x:c>
       <x:c r="I21" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J21" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K21" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L21" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M21" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N21" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O21" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P21" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="20" customHeight="1">
@@ -1787,8 +2355,10 @@
       <x:c r="C22" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D22" s="11" t="s">
-        <x:v>32</x:v>
+      <x:c r="D22" s="11" t="inlineStr">
+        <x:is>
+          <x:t>巡航攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E22" s="11" t="s">
         <x:v>25</x:v>
@@ -1804,6 +2374,29 @@
       </x:c>
       <x:c r="I22" s="11">
         <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J22" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K22" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L22" s="11">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="M22" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N22" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O22" s="12" t="inlineStr">
+        <x:is>
+          <x:t>-0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P22" s="11">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="20" customHeight="1">
@@ -1814,8 +2407,10 @@
       <x:c r="C23" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D23" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D23" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E23" s="11" t="s">
         <x:v>25</x:v>
@@ -1830,6 +2425,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I23" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J23" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K23" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L23" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M23" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N23" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O23" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P23" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1841,8 +2459,10 @@
       <x:c r="C24" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D24" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E24" s="11" t="s">
         <x:v>25</x:v>
@@ -1857,6 +2477,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I24" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J24" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K24" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L24" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M24" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N24" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O24" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P24" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1868,8 +2511,10 @@
       <x:c r="C25" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D25" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D25" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E25" s="11" t="s">
         <x:v>28</x:v>
@@ -1885,6 +2530,29 @@
       </x:c>
       <x:c r="I25" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J25" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K25" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L25" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M25" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N25" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O25" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P25" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="20" customHeight="1">
@@ -1895,8 +2563,10 @@
       <x:c r="C26" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D26" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D26" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E26" s="11" t="s">
         <x:v>25</x:v>
@@ -1912,6 +2582,29 @@
       </x:c>
       <x:c r="I26" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J26" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K26" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L26" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M26" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N26" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O26" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P26" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="20" customHeight="1">
@@ -1922,8 +2615,10 @@
       <x:c r="C27" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D27" s="11" t="s">
-        <x:v>32</x:v>
+      <x:c r="D27" s="11" t="inlineStr">
+        <x:is>
+          <x:t>巡航攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E27" s="11" t="s">
         <x:v>25</x:v>
@@ -1939,6 +2634,29 @@
       </x:c>
       <x:c r="I27" s="11">
         <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J27" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K27" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L27" s="11">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="M27" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N27" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O27" s="12" t="inlineStr">
+        <x:is>
+          <x:t>-0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P27" s="11">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="20" customHeight="1">
@@ -1949,8 +2667,10 @@
       <x:c r="C28" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D28" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D28" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E28" s="11" t="s">
         <x:v>25</x:v>
@@ -1965,6 +2685,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I28" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J28" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K28" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L28" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M28" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N28" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O28" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P28" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1976,8 +2719,10 @@
       <x:c r="C29" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D29" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D29" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E29" s="11" t="s">
         <x:v>25</x:v>
@@ -1992,6 +2737,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I29" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J29" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K29" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L29" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M29" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N29" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O29" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P29" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2003,8 +2771,10 @@
       <x:c r="C30" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D30" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D30" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E30" s="11" t="s">
         <x:v>28</x:v>
@@ -2020,6 +2790,29 @@
       </x:c>
       <x:c r="I30" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J30" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K30" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L30" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M30" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N30" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O30" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P30" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="20" customHeight="1">
@@ -2030,8 +2823,10 @@
       <x:c r="C31" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D31" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D31" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E31" s="11" t="s">
         <x:v>25</x:v>
@@ -2047,6 +2842,29 @@
       </x:c>
       <x:c r="I31" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J31" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K31" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L31" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M31" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N31" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O31" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P31" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="20" customHeight="1">
@@ -2057,8 +2875,10 @@
       <x:c r="C32" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D32" s="11" t="s">
-        <x:v>32</x:v>
+      <x:c r="D32" s="11" t="inlineStr">
+        <x:is>
+          <x:t>巡航攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E32" s="11" t="s">
         <x:v>25</x:v>
@@ -2074,6 +2894,29 @@
       </x:c>
       <x:c r="I32" s="11">
         <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J32" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K32" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L32" s="11">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="M32" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N32" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O32" s="12" t="inlineStr">
+        <x:is>
+          <x:t>-0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P32" s="11">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="20" customHeight="1">
@@ -2084,8 +2927,10 @@
       <x:c r="C33" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D33" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D33" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E33" s="11" t="s">
         <x:v>25</x:v>
@@ -2100,6 +2945,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I33" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J33" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K33" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L33" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M33" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N33" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O33" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P33" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2111,8 +2979,10 @@
       <x:c r="C34" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D34" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D34" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E34" s="11" t="s">
         <x:v>28</x:v>
@@ -2128,6 +2998,29 @@
       </x:c>
       <x:c r="I34" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J34" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K34" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L34" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M34" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N34" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O34" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P34" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="20" customHeight="1">
@@ -2138,8 +3031,10 @@
       <x:c r="C35" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D35" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D35" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E35" s="11" t="s">
         <x:v>25</x:v>
@@ -2154,6 +3049,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I35" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J35" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K35" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L35" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M35" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N35" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O35" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P35" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2165,8 +3083,10 @@
       <x:c r="C36" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D36" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D36" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E36" s="11" t="s">
         <x:v>28</x:v>
@@ -2182,6 +3102,29 @@
       </x:c>
       <x:c r="I36" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J36" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K36" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L36" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M36" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N36" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O36" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P36" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="20" customHeight="1">
@@ -2192,8 +3135,10 @@
       <x:c r="C37" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D37" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D37" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E37" s="11" t="s">
         <x:v>25</x:v>
@@ -2209,6 +3154,29 @@
       </x:c>
       <x:c r="I37" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J37" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K37" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L37" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M37" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N37" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O37" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P37" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="20" customHeight="1">
@@ -2219,8 +3187,10 @@
       <x:c r="C38" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D38" s="11" t="s">
-        <x:v>32</x:v>
+      <x:c r="D38" s="11" t="inlineStr">
+        <x:is>
+          <x:t>巡航攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E38" s="11" t="s">
         <x:v>25</x:v>
@@ -2236,6 +3206,29 @@
       </x:c>
       <x:c r="I38" s="11">
         <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J38" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K38" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L38" s="11">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="M38" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N38" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O38" s="12" t="inlineStr">
+        <x:is>
+          <x:t>-0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P38" s="11">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="20" customHeight="1">
@@ -2246,8 +3239,10 @@
       <x:c r="C39" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D39" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D39" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E39" s="11" t="s">
         <x:v>25</x:v>
@@ -2262,6 +3257,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I39" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J39" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K39" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L39" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M39" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N39" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O39" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P39" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2273,8 +3291,10 @@
       <x:c r="C40" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D40" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D40" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E40" s="11" t="s">
         <x:v>28</x:v>
@@ -2290,6 +3310,29 @@
       </x:c>
       <x:c r="I40" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J40" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K40" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L40" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M40" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N40" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O40" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P40" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="20" customHeight="1">
@@ -2300,8 +3343,10 @@
       <x:c r="C41" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D41" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D41" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E41" s="11" t="s">
         <x:v>25</x:v>
@@ -2316,6 +3361,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I41" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J41" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K41" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L41" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M41" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N41" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O41" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P41" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2327,8 +3395,10 @@
       <x:c r="C42" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D42" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D42" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E42" s="11" t="s">
         <x:v>28</x:v>
@@ -2344,6 +3414,29 @@
       </x:c>
       <x:c r="I42" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J42" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K42" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L42" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M42" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N42" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O42" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P42" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="20" customHeight="1">
@@ -2354,8 +3447,10 @@
       <x:c r="C43" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D43" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D43" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E43" s="11" t="s">
         <x:v>25</x:v>
@@ -2371,6 +3466,29 @@
       </x:c>
       <x:c r="I43" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J43" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K43" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L43" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M43" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N43" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O43" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P43" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="20" customHeight="1">
@@ -2381,8 +3499,10 @@
       <x:c r="C44" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D44" s="11" t="s">
-        <x:v>32</x:v>
+      <x:c r="D44" s="11" t="inlineStr">
+        <x:is>
+          <x:t>巡航攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E44" s="11" t="s">
         <x:v>25</x:v>
@@ -2398,6 +3518,29 @@
       </x:c>
       <x:c r="I44" s="11">
         <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J44" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K44" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L44" s="11">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="M44" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N44" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O44" s="12" t="inlineStr">
+        <x:is>
+          <x:t>-0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P44" s="11">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="20" customHeight="1">
@@ -2408,8 +3551,10 @@
       <x:c r="C45" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D45" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D45" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E45" s="11" t="s">
         <x:v>25</x:v>
@@ -2424,6 +3569,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I45" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J45" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K45" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L45" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M45" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N45" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O45" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P45" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2435,8 +3603,10 @@
       <x:c r="C46" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D46" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D46" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E46" s="11" t="s">
         <x:v>28</x:v>
@@ -2452,6 +3622,29 @@
       </x:c>
       <x:c r="I46" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J46" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K46" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L46" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M46" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N46" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O46" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P46" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="20" customHeight="1">
@@ -2462,8 +3655,10 @@
       <x:c r="C47" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D47" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D47" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E47" s="11" t="s">
         <x:v>25</x:v>
@@ -2479,6 +3674,29 @@
       </x:c>
       <x:c r="I47" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J47" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K47" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L47" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M47" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N47" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O47" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P47" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="20" customHeight="1">
@@ -2489,8 +3707,10 @@
       <x:c r="C48" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D48" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D48" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E48" s="11" t="s">
         <x:v>25</x:v>
@@ -2505,6 +3725,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I48" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J48" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K48" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L48" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M48" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N48" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O48" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P48" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2516,8 +3759,10 @@
       <x:c r="C49" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D49" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D49" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E49" s="11" t="s">
         <x:v>28</x:v>
@@ -2533,6 +3778,29 @@
       </x:c>
       <x:c r="I49" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J49" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K49" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L49" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M49" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N49" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O49" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P49" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="20" customHeight="1">
@@ -2543,8 +3811,10 @@
       <x:c r="C50" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D50" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D50" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E50" s="11" t="s">
         <x:v>25</x:v>
@@ -2560,6 +3830,29 @@
       </x:c>
       <x:c r="I50" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J50" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K50" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L50" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M50" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N50" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O50" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P50" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="20" customHeight="1">
@@ -2570,8 +3863,10 @@
       <x:c r="C51" s="11">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D51" s="11" t="s">
-        <x:v>32</x:v>
+      <x:c r="D51" s="11" t="inlineStr">
+        <x:is>
+          <x:t>巡航攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E51" s="11" t="s">
         <x:v>25</x:v>
@@ -2587,6 +3882,29 @@
       </x:c>
       <x:c r="I51" s="11">
         <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J51" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K51" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L51" s="11">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="M51" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N51" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O51" s="12" t="inlineStr">
+        <x:is>
+          <x:t>-0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P51" s="11">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="20" customHeight="1">
@@ -2597,8 +3915,10 @@
       <x:c r="C52" s="11">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D52" s="11" t="s">
-        <x:v>24</x:v>
+      <x:c r="D52" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E52" s="11" t="s">
         <x:v>25</x:v>
@@ -2613,6 +3933,29 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="I52" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J52" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K52" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L52" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M52" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N52" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O52" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P52" s="11">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2624,8 +3967,10 @@
       <x:c r="C53" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D53" s="11" t="s">
-        <x:v>27</x:v>
+      <x:c r="D53" s="11" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E53" s="11" t="s">
         <x:v>28</x:v>
@@ -2641,6 +3986,29 @@
       </x:c>
       <x:c r="I53" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J53" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K53" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L53" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M53" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N53" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O53" s="12" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P53" s="11">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="20" customHeight="1">
@@ -2651,8 +4019,10 @@
       <x:c r="C54" s="11">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D54" s="11" t="s">
-        <x:v>30</x:v>
+      <x:c r="D54" s="11" t="inlineStr">
+        <x:is>
+          <x:t>横向穿越</x:t>
+        </x:is>
       </x:c>
       <x:c r="E54" s="11" t="s">
         <x:v>25</x:v>
@@ -2668,6 +4038,29 @@
       </x:c>
       <x:c r="I54" s="11">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J54" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K54" s="11">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L54" s="11">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M54" s="11">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N54" s="11">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="O54" s="12" t="inlineStr">
+        <x:is>
+          <x:t>1,0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P54" s="11">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -2678,8 +4071,10 @@
       <x:c r="C55" s="7" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D55" s="7" t="str">
-        <x:v>直线</x:v>
+      <x:c r="D55" s="7" t="inlineStr">
+        <x:is>
+          <x:t>定点攻击</x:t>
+        </x:is>
       </x:c>
       <x:c r="E55" s="7" t="str">
         <x:v>横向编队</x:v>
@@ -2695,6 +4090,29 @@
       </x:c>
       <x:c r="I55" s="7" t="n">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="J55" s="7">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K55" s="7">
+        <x:v>400.0</x:v>
+      </x:c>
+      <x:c r="L55" s="7">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="M55" s="7">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="N55" s="7">
+        <x:v>0.6428571428571429</x:v>
+      </x:c>
+      <x:c r="O55" s="13" t="inlineStr">
+        <x:is>
+          <x:t>0.55,1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P55" s="7">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -2709,17 +4127,11 @@
       <x:c r="I56" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
-    <x:dataValidation type="list" sqref="D4:D1048576">
-      <x:formula1>"直线,斜向,蛇形,编队转向"</x:formula1>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D1048576">
+      <x:formula1>"定点攻击,横向穿越,巡航攻击"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="E4:E1048576">
-      <x:formula1>"横向编队,斜向编队"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="D55">
-      <x:formula1>"直线,斜向,蛇形,编队转向"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="E55">
+    <x:dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E4:E1048576">
       <x:formula1>"横向编队,斜向编队"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
